--- a/Investment_Portfolio_Tracker.xlsx
+++ b/Investment_Portfolio_Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holdings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Optimization" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Position Allocation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Holdings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Portfolio Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Position Allocation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Optimization" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -189,6 +189,136 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3333750" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4286250" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4286250" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>79</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4286250" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>99</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4286250" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -559,7 +689,7 @@
         <v>263.83</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>284.54</v>
+        <v>263.83</v>
       </c>
       <c r="F2" s="2">
         <f>C2*D2</f>
@@ -596,7 +726,7 @@
         <v>255.87</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>298.21</v>
+        <v>255.87</v>
       </c>
       <c r="F3" s="2">
         <f>C3*D3</f>
@@ -633,7 +763,7 @@
         <v>248.2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>267.29</v>
+        <v>248.2</v>
       </c>
       <c r="F4" s="2">
         <f>C4*D4</f>
@@ -670,7 +800,7 @@
         <v>59.46</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>56</v>
+        <v>59.46</v>
       </c>
       <c r="F5" s="2">
         <f>C5*D5</f>
@@ -707,7 +837,7 @@
         <v>43.39</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>43.46</v>
+        <v>43.39</v>
       </c>
       <c r="F6" s="2">
         <f>C6*D6</f>
@@ -744,7 +874,7 @@
         <v>175.84</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>195.78</v>
+        <v>175.84</v>
       </c>
       <c r="F7" s="2">
         <f>C7*D7</f>
@@ -781,7 +911,7 @@
         <v>326.38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>326.74</v>
+        <v>326.38</v>
       </c>
       <c r="F8" s="2">
         <f>C8*D8</f>
@@ -818,7 +948,7 @@
         <v>95.95</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>124.52</v>
+        <v>95.95</v>
       </c>
       <c r="F9" s="2">
         <f>C9*D9</f>
@@ -855,7 +985,7 @@
         <v>304.68</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>300.1</v>
+        <v>304.68</v>
       </c>
       <c r="F10" s="2">
         <f>C10*D10</f>
@@ -892,7 +1022,7 @@
         <v>153.54</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>429.38</v>
+        <v>153.54</v>
       </c>
       <c r="F11" s="2">
         <f>C11*D11</f>
@@ -929,7 +1059,7 @@
         <v>27.75</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>27.1</v>
+        <v>27.75</v>
       </c>
       <c r="F12" s="2">
         <f>C12*D12</f>
@@ -966,7 +1096,7 @@
         <v>3.7</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>5.23</v>
+        <v>3.7</v>
       </c>
       <c r="F13" s="2">
         <f>C13*D13</f>
@@ -1003,7 +1133,7 @@
         <v>45.88</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>49.9</v>
+        <v>45.88</v>
       </c>
       <c r="F14" s="2">
         <f>C14*D14</f>
@@ -1040,7 +1170,7 @@
         <v>43.81</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>71.3</v>
+        <v>43.81</v>
       </c>
       <c r="F15" s="2">
         <f>C15*D15</f>
@@ -1077,7 +1207,7 @@
         <v>126.56</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>235.5</v>
+        <v>126.56</v>
       </c>
       <c r="F16" s="2">
         <f>C16*D16</f>
@@ -1114,7 +1244,7 @@
         <v>66.98999999999999</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>132.29</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="F17" s="2">
         <f>C17*D17</f>
@@ -1151,7 +1281,7 @@
         <v>14.27</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>25.82</v>
+        <v>14.27</v>
       </c>
       <c r="F18" s="2">
         <f>C18*D18</f>
@@ -1188,7 +1318,7 @@
         <v>16.49</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>24.66</v>
+        <v>16.49</v>
       </c>
       <c r="F19" s="2">
         <f>C19*D19</f>
@@ -1343,183 +1473,317 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>📊 PORTFOLIO OPTIMIZATION DASHBOARD</t>
-        </is>
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Current Value</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>Current %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="B2" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A2,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C2" s="3">
+        <f>B2/$B$20</f>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>CURRENT METRICS</t>
-        </is>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B3" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A3,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>B3/$B$20</f>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Portfolio Value: $2,055.82</t>
-        </is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B4" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A4,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>B4/$B$20</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Click the button below to run portfolio_optimizer.py</t>
-        </is>
+          <t>JEPI</t>
+        </is>
+      </c>
+      <c r="B5" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A5,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C5" s="3">
+        <f>B5/$B$20</f>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>This will fetch real-time prices and update all visualizations</t>
-        </is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="B6" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A6,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>B6/$B$20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="B7" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A7,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C7" s="3">
+        <f>B7/$B$20</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>INSTRUCTIONS</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B8" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A8,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>B8/$B$20</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1. Make sure you have Python 3.8+ installed</t>
-        </is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B9" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A9,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>B9/$B$20</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2. Install required packages: pip install yfinance pandas numpy scipy matplotlib seaborn openpyxl pillow</t>
-        </is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B10" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A10,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C10" s="3">
+        <f>B10/$B$20</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3. Open Terminal/Command Prompt and navigate to your Personal Investment Tracker folder</t>
-        </is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B11" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A11,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>B11/$B$20</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4. Run: python3 portfolio_optimizer.py</t>
-        </is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="B12" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A12,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C12" s="3">
+        <f>B12/$B$20</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5. Wait for it to complete (~30 seconds) - it will update this file automatically</t>
-        </is>
+          <t>LYG</t>
+        </is>
+      </c>
+      <c r="B13" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A13,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>B13/$B$20</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B14" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A14,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C14" s="3">
+        <f>B14/$B$20</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>The script will:</t>
-        </is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="B15" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A15,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C15" s="3">
+        <f>B15/$B$20</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✓ Fetch real-time prices from Yahoo Finance</t>
-        </is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B16" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A16,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C16" s="3">
+        <f>B16/$B$20</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✓ Generate 5 professional visualizations (charts)</t>
-        </is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="B17" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A17,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C17" s="3">
+        <f>B17/$B$20</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✓ Calculate optimized portfolio allocation</t>
-        </is>
+          <t>NTGR</t>
+        </is>
+      </c>
+      <c r="B18" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A18,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C18" s="3">
+        <f>B18/$B$20</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✓ Show sensitivity analysis for different scenarios</t>
-        </is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B19" s="2">
+        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A19,Holdings!$A$2:$A$19,0))</f>
+        <v/>
+      </c>
+      <c r="C19" s="3">
+        <f>B19/$B$20</f>
+        <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ✓ Update this Dashboard with all KPIs</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>VISUALIZATION SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>📊 Sector Concentration: Pie chart showing allocation by industry</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>📈 Current vs Optimal: Bar charts comparing your allocation to recommended allocation</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>📉 Portfolio Growth: 1-year performance chart for each stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>🎯 Sensitivity Analysis: Expected returns for different allocation strategies</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>⚠️  Risk-Return Profile: Scatter plot showing risk vs return of each position</t>
-        </is>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B20" s="5">
+        <f>SUM(B2:B19)</f>
+        <v/>
+      </c>
+      <c r="C20" s="6">
+        <f>SUM(C2:C19)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A3:D3"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1530,317 +1794,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>Symbol</t>
-        </is>
-      </c>
-      <c r="B1" s="12" t="inlineStr">
-        <is>
-          <t>Current Value</t>
-        </is>
-      </c>
-      <c r="C1" s="12" t="inlineStr">
-        <is>
-          <t>Current %</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="B2" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A2,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C2" s="3">
-        <f>B2/$B$20</f>
-        <v/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>📊 PORTFOLIO OPTIMIZATION DASHBOARD</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="B3" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A3,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C3" s="3">
-        <f>B3/$B$20</f>
-        <v/>
+          <t>KEY METRICS</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="B4" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A4,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C4" s="3">
-        <f>B4/$B$20</f>
-        <v/>
+          <t>Portfolio Value: $1,616.01</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JEPI</t>
-        </is>
-      </c>
-      <c r="B5" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A5,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C5" s="3">
-        <f>B5/$B$20</f>
-        <v/>
+          <t>Total Gain/Loss: $0.00</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLG</t>
-        </is>
-      </c>
-      <c r="B6" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A6,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C6" s="3">
-        <f>B6/$B$20</f>
-        <v/>
+          <t>Return %: 0.00%</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORCL</t>
-        </is>
-      </c>
-      <c r="B7" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A7,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C7" s="3">
-        <f>B7/$B$20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B8" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A8,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C8" s="3">
-        <f>B8/$B$20</f>
-        <v/>
+          <t>Updated: 2026-05-15 19:07:41</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B9" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A9,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C9" s="3">
-        <f>B9/$B$20</f>
-        <v/>
+          <t>PORTFOLIO METRICS</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JPM</t>
-        </is>
-      </c>
-      <c r="B10" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A10,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C10" s="3">
-        <f>B10/$B$20</f>
-        <v/>
+          <t>Current Annual Return: 3780.00%</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B11" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A11,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C11" s="3">
-        <f>B11/$B$20</f>
-        <v/>
+          <t>Current Risk (Volatility): 1093.16%</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="B12" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A12,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C12" s="3">
-        <f>B12/$B$20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>LYG</t>
-        </is>
-      </c>
-      <c r="B13" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A13,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C13" s="3">
-        <f>B13/$B$20</f>
-        <v/>
+          <t>Current Sharpe Ratio: 3.46</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="B14" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A14,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C14" s="3">
-        <f>B14/$B$20</f>
-        <v/>
+          <t>OPTIMAL ALLOCATION METRICS</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="B15" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A15,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C15" s="3">
-        <f>B15/$B$20</f>
-        <v/>
+          <t>Optimal Annual Return: 3780.00%</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B16" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A16,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C16" s="3">
-        <f>B16/$B$20</f>
-        <v/>
+          <t>Optimal Risk (Volatility): 836.90%</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="B17" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A17,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C17" s="3">
-        <f>B17/$B$20</f>
-        <v/>
+          <t>Optimal Sharpe Ratio: 4.52</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NTGR</t>
-        </is>
-      </c>
-      <c r="B18" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A18,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C18" s="3">
-        <f>B18/$B$20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="B19" s="2">
-        <f>INDEX(Holdings!$G$2:$G$19,MATCH(A19,Holdings!$A$2:$A$19,0))</f>
-        <v/>
-      </c>
-      <c r="C19" s="3">
-        <f>B19/$B$20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B20" s="5">
-        <f>SUM(B2:B19)</f>
-        <v/>
-      </c>
-      <c r="C20" s="6">
-        <f>SUM(C2:C19)</f>
-        <v/>
+          <t>Improvement in Sharpe: 30.6%</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Investment_Portfolio_Tracker.xlsx
+++ b/Investment_Portfolio_Tracker.xlsx
@@ -689,7 +689,7 @@
         <v>263.83</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>263.83</v>
+        <v>278.2250061035156</v>
       </c>
       <c r="F2" s="2">
         <f>C2*D2</f>
@@ -726,7 +726,7 @@
         <v>255.87</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>255.87</v>
+        <v>300.4500122070312</v>
       </c>
       <c r="F3" s="2">
         <f>C3*D3</f>
@@ -763,7 +763,7 @@
         <v>248.2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>248.2</v>
+        <v>263.4400024414062</v>
       </c>
       <c r="F4" s="2">
         <f>C4*D4</f>
@@ -800,7 +800,7 @@
         <v>59.46</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>59.46</v>
+        <v>55.85010147094727</v>
       </c>
       <c r="F5" s="2">
         <f>C5*D5</f>
@@ -837,7 +837,7 @@
         <v>43.39</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>43.39</v>
+        <v>42.47499847412109</v>
       </c>
       <c r="F6" s="2">
         <f>C6*D6</f>
@@ -874,7 +874,7 @@
         <v>175.84</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>175.84</v>
+        <v>194.6750030517578</v>
       </c>
       <c r="F7" s="2">
         <f>C7*D7</f>
@@ -911,7 +911,7 @@
         <v>326.38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>326.38</v>
+        <v>424.1099853515625</v>
       </c>
       <c r="F8" s="2">
         <f>C8*D8</f>
@@ -948,7 +948,7 @@
         <v>95.95</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>95.95</v>
+        <v>123.7649993896484</v>
       </c>
       <c r="F9" s="2">
         <f>C9*D9</f>
@@ -985,7 +985,7 @@
         <v>304.68</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>304.68</v>
+        <v>297.760009765625</v>
       </c>
       <c r="F10" s="2">
         <f>C10*D10</f>
@@ -1022,7 +1022,7 @@
         <v>153.54</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>153.54</v>
+        <v>732.25</v>
       </c>
       <c r="F11" s="2">
         <f>C11*D11</f>
@@ -1059,7 +1059,7 @@
         <v>27.75</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>27.75</v>
+        <v>27.03499984741211</v>
       </c>
       <c r="F12" s="2">
         <f>C12*D12</f>
@@ -1096,7 +1096,7 @@
         <v>3.7</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>3.7</v>
+        <v>5.054999828338623</v>
       </c>
       <c r="F13" s="2">
         <f>C13*D13</f>
@@ -1133,7 +1133,7 @@
         <v>45.88</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>45.88</v>
+        <v>49.49499893188477</v>
       </c>
       <c r="F14" s="2">
         <f>C14*D14</f>
@@ -1170,7 +1170,7 @@
         <v>43.81</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>43.81</v>
+        <v>70.51999664306641</v>
       </c>
       <c r="F15" s="2">
         <f>C15*D15</f>
@@ -1207,7 +1207,7 @@
         <v>126.56</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>126.56</v>
+        <v>227.5500946044922</v>
       </c>
       <c r="F16" s="2">
         <f>C16*D16</f>
@@ -1244,7 +1244,7 @@
         <v>66.98999999999999</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>66.98999999999999</v>
+        <v>131.2599945068359</v>
       </c>
       <c r="F17" s="2">
         <f>C17*D17</f>
@@ -1281,7 +1281,7 @@
         <v>14.27</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>14.27</v>
+        <v>24.98999977111816</v>
       </c>
       <c r="F18" s="2">
         <f>C18*D18</f>
@@ -1318,7 +1318,7 @@
         <v>16.49</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>16.49</v>
+        <v>24.22500038146973</v>
       </c>
       <c r="F19" s="2">
         <f>C19*D19</f>
@@ -1814,28 +1814,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Portfolio Value: $1,616.01</t>
+          <t>Portfolio Value: $2,279.06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Total Gain/Loss: $0.00</t>
+          <t>Total Gain/Loss: $663.05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Return %: 0.00%</t>
+          <t>Return %: 41.03%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Updated: 2026-05-15 19:07:41</t>
+          <t>Updated: 2026-05-15 19:19:54</t>
         </is>
       </c>
     </row>
@@ -1849,21 +1849,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Current Annual Return: 3780.00%</t>
+          <t>Current Annual Return: 27.35%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Current Risk (Volatility): 1093.16%</t>
+          <t>Current Risk (Volatility): 14.58%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Current Sharpe Ratio: 3.46</t>
+          <t>Current Sharpe Ratio: 1.88</t>
         </is>
       </c>
     </row>
@@ -1877,28 +1877,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Optimal Annual Return: 3780.00%</t>
+          <t>Optimal Annual Return: 86.58%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Optimal Risk (Volatility): 836.90%</t>
+          <t>Optimal Risk (Volatility): 18.88%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Optimal Sharpe Ratio: 4.52</t>
+          <t>Optimal Sharpe Ratio: 4.58</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Improvement in Sharpe: 30.6%</t>
+          <t>Improvement in Sharpe: 144.4%</t>
         </is>
       </c>
     </row>

--- a/Investment_Portfolio_Tracker.xlsx
+++ b/Investment_Portfolio_Tracker.xlsx
@@ -689,7 +689,7 @@
         <v>263.83</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>278.2250061035156</v>
+        <v>277.6000061035156</v>
       </c>
       <c r="F2" s="2">
         <f>C2*D2</f>
@@ -726,7 +726,7 @@
         <v>255.87</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>300.4500122070312</v>
+        <v>300.2300109863281</v>
       </c>
       <c r="F3" s="2">
         <f>C3*D3</f>
@@ -763,7 +763,7 @@
         <v>248.2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>263.4400024414062</v>
+        <v>264.1400146484375</v>
       </c>
       <c r="F4" s="2">
         <f>C4*D4</f>
@@ -800,7 +800,7 @@
         <v>59.46</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>55.85010147094727</v>
+        <v>55.88999938964844</v>
       </c>
       <c r="F5" s="2">
         <f>C5*D5</f>
@@ -837,7 +837,7 @@
         <v>43.39</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>42.47499847412109</v>
+        <v>42.45000076293945</v>
       </c>
       <c r="F6" s="2">
         <f>C6*D6</f>
@@ -874,7 +874,7 @@
         <v>175.84</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>194.6750030517578</v>
+        <v>192.9499969482422</v>
       </c>
       <c r="F7" s="2">
         <f>C7*D7</f>
@@ -911,7 +911,7 @@
         <v>326.38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>424.1099853515625</v>
+        <v>421.9200134277344</v>
       </c>
       <c r="F8" s="2">
         <f>C8*D8</f>
@@ -948,7 +948,7 @@
         <v>95.95</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>123.7649993896484</v>
+        <v>123.4199981689453</v>
       </c>
       <c r="F9" s="2">
         <f>C9*D9</f>
@@ -985,7 +985,7 @@
         <v>304.68</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>297.760009765625</v>
+        <v>297.8099975585938</v>
       </c>
       <c r="F10" s="2">
         <f>C10*D10</f>
@@ -1022,7 +1022,7 @@
         <v>153.54</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>732.25</v>
+        <v>724.6599731445312</v>
       </c>
       <c r="F11" s="2">
         <f>C11*D11</f>
@@ -1059,7 +1059,7 @@
         <v>27.75</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>27.03499984741211</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="F12" s="2">
         <f>C12*D12</f>
@@ -1096,7 +1096,7 @@
         <v>3.7</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>5.054999828338623</v>
+        <v>5.050000190734863</v>
       </c>
       <c r="F13" s="2">
         <f>C13*D13</f>
@@ -1133,7 +1133,7 @@
         <v>45.88</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>49.49499893188477</v>
+        <v>49.77000045776367</v>
       </c>
       <c r="F14" s="2">
         <f>C14*D14</f>
@@ -1170,7 +1170,7 @@
         <v>43.81</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>70.51999664306641</v>
+        <v>70.23000335693359</v>
       </c>
       <c r="F15" s="2">
         <f>C15*D15</f>
@@ -1207,7 +1207,7 @@
         <v>126.56</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>227.5500946044922</v>
+        <v>225.3200073242188</v>
       </c>
       <c r="F16" s="2">
         <f>C16*D16</f>
@@ -1244,7 +1244,7 @@
         <v>66.98999999999999</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>131.2599945068359</v>
+        <v>131.4499969482422</v>
       </c>
       <c r="F17" s="2">
         <f>C17*D17</f>
@@ -1281,7 +1281,7 @@
         <v>14.27</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>24.98999977111816</v>
+        <v>24.75</v>
       </c>
       <c r="F18" s="2">
         <f>C18*D18</f>
@@ -1318,7 +1318,7 @@
         <v>16.49</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>24.22500038146973</v>
+        <v>24.03000068664551</v>
       </c>
       <c r="F19" s="2">
         <f>C19*D19</f>
@@ -1814,28 +1814,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Portfolio Value: $2,279.06</t>
+          <t>Portfolio Value: $2,268.08</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Total Gain/Loss: $663.05</t>
+          <t>Total Gain/Loss: $652.07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Return %: 41.03%</t>
+          <t>Return %: 40.35%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Updated: 2026-05-15 19:19:54</t>
+          <t>Updated: 2026-05-16 20:55:15</t>
         </is>
       </c>
     </row>
@@ -1849,21 +1849,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Current Annual Return: 27.35%</t>
+          <t>Current Annual Return: 26.44%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Current Risk (Volatility): 14.58%</t>
+          <t>Current Risk (Volatility): 14.61%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Current Sharpe Ratio: 1.88</t>
+          <t>Current Sharpe Ratio: 1.81</t>
         </is>
       </c>
     </row>
@@ -1877,28 +1877,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Optimal Annual Return: 86.58%</t>
+          <t>Optimal Annual Return: 87.05%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Optimal Risk (Volatility): 18.88%</t>
+          <t>Optimal Risk (Volatility): 19.29%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Optimal Sharpe Ratio: 4.58</t>
+          <t>Optimal Sharpe Ratio: 4.51</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Improvement in Sharpe: 144.4%</t>
+          <t>Improvement in Sharpe: 149.4%</t>
         </is>
       </c>
     </row>
